--- a/www/flightdata/xlsx/eoss-320.xlsx
+++ b/www/flightdata/xlsx/eoss-320.xlsx
@@ -3435,7 +3435,7 @@
         <v>28393.64</v>
       </c>
       <c r="I2">
-        <v>594</v>
+        <v>436</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
